--- a/docs/test-data/tire-import/02-mixed-cases.xlsx
+++ b/docs/test-data/tire-import/02-mixed-cases.xlsx
@@ -64,13 +64,7 @@
     <t>ผ่าน · ตัวพิมพ์เล็ก/ช่องว่างเกินต้องจับคู่ได้</t>
   </si>
   <si>
-    <t>GOODYEAR</t>
-  </si>
-  <si>
-    <t>KMAX S</t>
-  </si>
-  <si>
-    <t>295/80 R22.5</t>
+    <t>11R22.5 16 PR</t>
   </si>
   <si>
     <t>SEED1020-M003</t>
@@ -79,15 +73,6 @@
     <t>ผ่าน · ขนาดมีช่องว่างคั่น</t>
   </si>
   <si>
-    <t>HANKOOK</t>
-  </si>
-  <si>
-    <t>AH35</t>
-  </si>
-  <si>
-    <t>315/80R22.5</t>
-  </si>
-  <si>
     <t>seed1020-m004</t>
   </si>
   <si>
@@ -133,7 +118,7 @@
     <t>SEED1020-M007</t>
   </si>
   <si>
-    <t>ผ่าน (Premium) · สร้างยี่ห้อ/รุ่นใหม่ให้บริษัท · Standard = ไม่ผ่าน</t>
+    <t>ไม่ผ่าน · ไม่มียี่ห้อนี้ในข้อมูลยาง ระบบไม่สร้างให้</t>
   </si>
   <si>
     <t>SAILUN</t>
@@ -145,7 +130,7 @@
     <t>SEED1020-M008</t>
   </si>
   <si>
-    <t>ผ่าน (Premium) · รุ่นกลางที่ไม่ได้รับสิทธิ์ จะสร้างเป็นของบริษัท</t>
+    <t>ไม่ผ่าน · รุ่นกลางที่บริษัทไม่ได้รับสิทธิ์</t>
   </si>
   <si>
     <t>ไม่ผ่าน · ยังไม่ได้กรอก ซีรีย์</t>
@@ -245,9 +230,6 @@
   </si>
   <si>
     <t>แถวว่าง · ต้องถูกข้าม ไม่นับเป็นแถว</t>
-  </si>
-  <si>
-    <t>295/80R22.5</t>
   </si>
   <si>
     <t>SEED1020-M024</t>
@@ -373,104 +355,104 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -484,7 +466,7 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +477,10 @@
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F11" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
@@ -509,10 +491,10 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -523,10 +505,10 @@
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14">
@@ -543,7 +525,7 @@
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -557,10 +539,10 @@
         <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -574,10 +556,10 @@
         <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -591,10 +573,10 @@
         <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -608,10 +590,10 @@
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F18" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -625,41 +607,41 @@
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
         <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E21" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F21" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22">
@@ -673,55 +655,55 @@
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E22" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F22" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F23" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24">
       <c r="F24" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E25" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F25" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
